--- a/docs/CRM接口测试用例.xlsx
+++ b/docs/CRM接口测试用例.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="620" firstSheet="1"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="620" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="场景测试用例" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="168">
   <si>
     <t>ID</t>
   </si>
@@ -126,7 +126,7 @@
   <si>
     <t>{
     "username": "admin",
-    "password": "HM_2023_test",
+    "password": "123456",
     "code": "2",
     "uuid": "xxxxxx"
 }</t>
@@ -214,7 +214,7 @@
   <si>
     <t>{
     "username": "",
-    "password": "HM_2023_test",
+    "password": "123456",
     "code": "2",
     "uuid": "xxxxxx"
 }</t>
@@ -233,40 +233,6 @@
   </si>
   <si>
     <t>1、验证码获取成功</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">{
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">    "username": "admin",
-    "password": "HM_2023_test",</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-    "code": "2",
-    "uuid": "xxxxxx"
-}</t>
-    </r>
   </si>
   <si>
     <t>{
@@ -285,55 +251,12 @@
     <t>P3</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">{
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">    "username": "admin",
-    "password": "HM_2023_test",</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-    "code": "2",</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-    "uuid": ""</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-}</t>
-    </r>
+    <t>{
+    "username": "admin",
+    "password": "123456",
+    "code": "2",
+    "uuid": ""
+}</t>
   </si>
   <si>
     <r>
@@ -374,55 +297,12 @@
     <t>登录失败（code为空）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">{
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">    "username": "admin",
-    "password": "HM_2023_test",</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">    "code": "",</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>{
+    "username": "admin",
+    "password": "123456",
+    "code": "",
     "uuid": "xxxxxx"
 }</t>
-    </r>
   </si>
   <si>
     <t>kdtx-loginAPI-004</t>
@@ -431,112 +311,18 @@
     <t>登录失败（code值与图片接口返回不一致，如：3）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">{
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">    "username": "admin",
-    "password": "HM_2023_test",</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">    "code": "3",</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>{
+    "username": "admin",
+    "password": "123456",
+    "code": "3",
     "uuid": "xxxxxx"
 }</t>
-    </r>
   </si>
   <si>
     <t>kdtx-loginAPI-005</t>
   </si>
   <si>
     <t>登录失败（code值过期）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">{
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">    "username": "admin",
-    "password": "HM_2023_test",</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">    "code": "2",</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-    "uuid": "xxxxxx"
-}</t>
-    </r>
   </si>
   <si>
     <t>kdtx-loginAPI-006</t>
@@ -1911,7 +1697,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1939,15 +1725,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1975,12 +1752,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2001,9 +1772,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2553,299 +2321,299 @@
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="J1" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="23" t="s">
+      <c r="K1" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="23" t="s">
+      <c r="L1" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="23" t="s">
+      <c r="M1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="23" t="s">
+      <c r="N1" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="23" t="s">
+      <c r="O1" s="18" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" ht="104.4" spans="1:15">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="H2" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="26" t="s">
+      <c r="J2" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="26">
+      <c r="L2" s="21">
         <v>200</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
     </row>
-    <row r="3" ht="121.8" spans="1:15">
-      <c r="A3" s="28"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26" t="s">
+    <row r="3" ht="104.4" spans="1:15">
+      <c r="A3" s="23"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="26"/>
-      <c r="G3" s="27" t="s">
+      <c r="F3" s="21"/>
+      <c r="G3" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="H3" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="J3" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="21" t="s">
+      <c r="K3" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="21">
         <v>200</v>
       </c>
-      <c r="M3" s="21" t="s">
+      <c r="M3" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
     </row>
-    <row r="4" ht="121.8" spans="1:15">
-      <c r="A4" s="28"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26" t="s">
+    <row r="4" ht="104.4" spans="1:15">
+      <c r="A4" s="23"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="26"/>
-      <c r="G4" s="27" t="s">
+      <c r="F4" s="21"/>
+      <c r="G4" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="H4" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="J4" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="21" t="s">
+      <c r="K4" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="26">
+      <c r="L4" s="21">
         <v>200</v>
       </c>
-      <c r="M4" s="21" t="s">
+      <c r="M4" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="N4" s="21"/>
-      <c r="O4" s="21"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
     </row>
     <row r="5" ht="104.4" spans="1:15">
-      <c r="A5" s="28"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26" t="s">
+      <c r="A5" s="23"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="27" t="s">
+      <c r="F5" s="21"/>
+      <c r="G5" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="26" t="s">
+      <c r="H5" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="6">
         <v>200</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="M5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="N5" s="21"/>
-      <c r="O5" s="21"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
     </row>
-    <row r="6" ht="191.4" spans="1:15">
-      <c r="A6" s="29"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26" t="s">
+    <row r="6" ht="174" spans="1:15">
+      <c r="A6" s="24"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="26"/>
-      <c r="G6" s="27" t="s">
+      <c r="F6" s="21"/>
+      <c r="G6" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="26" t="s">
+      <c r="H6" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="6">
         <v>200</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="N6" s="21"/>
-      <c r="O6" s="21"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
     </row>
     <row r="7" ht="104.4" spans="1:15">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="G7" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="26" t="s">
+      <c r="H7" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="6">
         <v>200</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="N7" s="21"/>
-      <c r="O7" s="21"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
     </row>
-    <row r="8" ht="121.8" spans="1:15">
-      <c r="A8" s="26"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26" t="s">
+    <row r="8" ht="104.4" spans="1:15">
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="26"/>
-      <c r="G8" s="30" t="s">
+      <c r="F8" s="21"/>
+      <c r="G8" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="26" t="s">
+      <c r="H8" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="6">
         <v>200</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M8" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="N8" s="21"/>
-      <c r="O8" s="21"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2881,455 +2649,455 @@
   <dimension ref="A1:O10"/>
   <sheetFormatPr defaultColWidth="13.1388888888889" defaultRowHeight="17.4"/>
   <cols>
-    <col min="1" max="1" width="22.3333333333333" style="13" customWidth="1"/>
-    <col min="2" max="2" width="13.1388888888889" style="12" customWidth="1"/>
-    <col min="3" max="3" width="57.4444444444444" style="12" customWidth="1"/>
-    <col min="4" max="4" width="11.6666666666667" style="12" customWidth="1"/>
-    <col min="5" max="5" width="12.4907407407407" style="12" customWidth="1"/>
-    <col min="6" max="6" width="21.8888888888889" style="12" customWidth="1"/>
-    <col min="7" max="7" width="43" style="12" customWidth="1"/>
-    <col min="8" max="8" width="13.1388888888889" style="12" customWidth="1"/>
-    <col min="9" max="9" width="40.1111111111111" style="12" customWidth="1"/>
-    <col min="10" max="10" width="13.1388888888889" style="12" customWidth="1"/>
-    <col min="11" max="11" width="37.7777777777778" style="12" customWidth="1"/>
-    <col min="12" max="12" width="13.1388888888889" style="12" customWidth="1"/>
-    <col min="13" max="13" width="34" style="12" customWidth="1"/>
-    <col min="14" max="16384" width="13.1388888888889" style="12" customWidth="1"/>
+    <col min="1" max="1" width="22.3333333333333" style="10" customWidth="1"/>
+    <col min="2" max="2" width="13.1388888888889" style="9" customWidth="1"/>
+    <col min="3" max="3" width="57.4444444444444" style="9" customWidth="1"/>
+    <col min="4" max="4" width="11.6666666666667" style="9" customWidth="1"/>
+    <col min="5" max="5" width="12.4907407407407" style="9" customWidth="1"/>
+    <col min="6" max="6" width="21.8888888888889" style="9" customWidth="1"/>
+    <col min="7" max="7" width="43" style="9" customWidth="1"/>
+    <col min="8" max="8" width="13.1388888888889" style="9" customWidth="1"/>
+    <col min="9" max="9" width="40.1111111111111" style="9" customWidth="1"/>
+    <col min="10" max="10" width="13.1388888888889" style="9" customWidth="1"/>
+    <col min="11" max="11" width="37.7777777777778" style="9" customWidth="1"/>
+    <col min="12" max="12" width="13.1388888888889" style="9" customWidth="1"/>
+    <col min="13" max="13" width="34" style="9" customWidth="1"/>
+    <col min="14" max="16384" width="13.1388888888889" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="12" customFormat="1" ht="34.8" spans="1:15">
-      <c r="A1" s="14" t="s">
+    <row r="1" s="9" customFormat="1" ht="34.8" spans="1:15">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" s="12" customFormat="1" ht="104.4" spans="1:15">
-      <c r="A2" s="17" t="s">
+    <row r="2" s="9" customFormat="1" ht="104.4" spans="1:15">
+      <c r="A2" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="14">
+        <v>200</v>
+      </c>
+      <c r="M2" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="L2" s="17">
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+    </row>
+    <row r="3" s="9" customFormat="1" ht="104.4" spans="1:15">
+      <c r="A3" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="L3" s="14">
         <v>200</v>
       </c>
-      <c r="M2" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
+      <c r="M3" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
     </row>
-    <row r="3" s="12" customFormat="1" ht="104.4" spans="1:15">
-      <c r="A3" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="17" t="s">
+    <row r="4" s="9" customFormat="1" ht="104.4" spans="1:15">
+      <c r="A4" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C4" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="17" t="s">
+      <c r="E4" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F4" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G4" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H4" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I4" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="J4" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="20" t="s">
+      <c r="K4" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="L4" s="14">
+        <v>200</v>
+      </c>
+      <c r="M4" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="L3" s="17">
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+    </row>
+    <row r="5" s="9" customFormat="1" ht="104.4" spans="1:15">
+      <c r="A5" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="L5" s="14">
         <v>200</v>
       </c>
-      <c r="M3" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="N3" s="22"/>
-      <c r="O3" s="18"/>
+      <c r="M5" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
     </row>
-    <row r="4" s="12" customFormat="1" ht="104.4" spans="1:15">
-      <c r="A4" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="17" t="s">
+    <row r="6" s="9" customFormat="1" ht="104.4" spans="1:15">
+      <c r="A6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="17" t="s">
+      <c r="C6" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F6" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G6" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H6" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="20" t="s">
+      <c r="I6" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="17" t="s">
+      <c r="J6" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="L4" s="17">
+      <c r="K6" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="14">
         <v>200</v>
       </c>
-      <c r="M4" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="N4" s="22"/>
-      <c r="O4" s="18"/>
+      <c r="M6" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
     </row>
-    <row r="5" s="12" customFormat="1" ht="104.4" spans="1:15">
-      <c r="A5" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" s="17" t="s">
+    <row r="7" s="9" customFormat="1" ht="104.4" spans="1:15">
+      <c r="A7" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="17" t="s">
+      <c r="C7" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F7" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G7" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H7" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I7" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="17" t="s">
+      <c r="J7" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="L5" s="17">
+      <c r="K7" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="L7" s="14">
         <v>200</v>
       </c>
-      <c r="M5" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="N5" s="22"/>
-      <c r="O5" s="18"/>
+      <c r="M7" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
     </row>
-    <row r="6" s="12" customFormat="1" ht="104.4" spans="1:15">
-      <c r="A6" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="17" t="s">
+    <row r="8" s="9" customFormat="1" ht="104.4" spans="1:15">
+      <c r="A8" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="17" t="s">
+      <c r="C8" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F8" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G8" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H8" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I8" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J6" s="17" t="s">
+      <c r="J8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="K6" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="L6" s="17">
+      <c r="K8" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="L8" s="14">
         <v>200</v>
       </c>
-      <c r="M6" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="N6" s="22"/>
-      <c r="O6" s="18"/>
+      <c r="M8" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
     </row>
-    <row r="7" s="12" customFormat="1" ht="104.4" spans="1:15">
-      <c r="A7" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" s="17" t="s">
+    <row r="9" s="9" customFormat="1" ht="104.4" spans="1:15">
+      <c r="A9" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C9" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="L9" s="14">
+        <v>200</v>
+      </c>
+      <c r="M9" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D7" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+    </row>
+    <row r="10" s="9" customFormat="1" ht="104.4" spans="1:15">
+      <c r="A10" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="C10" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G10" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H10" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I10" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="17" t="s">
+      <c r="J10" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="L7" s="17">
+      <c r="K10" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L10" s="14">
         <v>200</v>
       </c>
-      <c r="M7" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="N7" s="22"/>
-      <c r="O7" s="18"/>
-    </row>
-    <row r="8" s="12" customFormat="1" ht="104.4" spans="1:15">
-      <c r="A8" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="K8" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="L8" s="17">
-        <v>200</v>
-      </c>
-      <c r="M8" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="N8" s="18"/>
-      <c r="O8" s="18"/>
-    </row>
-    <row r="9" s="12" customFormat="1" ht="104.4" spans="1:15">
-      <c r="A9" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="J9" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="L9" s="17">
-        <v>200</v>
-      </c>
-      <c r="M9" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
-    </row>
-    <row r="10" s="12" customFormat="1" ht="104.4" spans="1:15">
-      <c r="A10" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="K10" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="L10" s="17">
-        <v>200</v>
-      </c>
-      <c r="M10" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="N10" s="18"/>
-      <c r="O10" s="18"/>
+      <c r="M10" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3401,7 +3169,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>10</v>
@@ -3421,1083 +3189,1083 @@
     </row>
     <row r="2" ht="121.8" spans="1:15">
       <c r="A2" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>86</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>52</v>
       </c>
       <c r="E2" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J2" s="6" t="s">
         <v>28</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L2" s="6">
         <v>200</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O2" s="7"/>
     </row>
     <row r="3" ht="121.8" spans="1:15">
       <c r="A3" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>52</v>
       </c>
       <c r="E3" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L3" s="6">
         <v>200</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O3" s="7"/>
     </row>
     <row r="4" ht="156.6" spans="1:15">
       <c r="A4" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>52</v>
       </c>
       <c r="E4" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J4" s="6" t="s">
         <v>28</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L4" s="6">
         <v>200</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O4" s="7"/>
     </row>
     <row r="5" ht="139.2" spans="1:15">
       <c r="A5" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>52</v>
       </c>
       <c r="E5" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>28</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L5" s="6">
         <v>200</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O5" s="7"/>
     </row>
     <row r="6" ht="139.2" spans="1:15">
       <c r="A6" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>52</v>
       </c>
       <c r="E6" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>28</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L6" s="6">
         <v>200</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O6" s="7"/>
     </row>
     <row r="7" ht="139.2" spans="1:15">
       <c r="A7" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>52</v>
       </c>
       <c r="E7" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="L7" s="10">
+      <c r="K7" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="L7" s="6">
         <v>200</v>
       </c>
-      <c r="M7" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>92</v>
+      <c r="M7" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="O7" s="7"/>
     </row>
     <row r="8" ht="139.2" spans="1:15">
       <c r="A8" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>52</v>
       </c>
       <c r="E8" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K8" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="L8" s="10">
+      <c r="K8" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="L8" s="6">
         <v>200</v>
       </c>
-      <c r="M8" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>92</v>
+      <c r="M8" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="O8" s="7"/>
     </row>
     <row r="9" ht="139.2" spans="1:15">
       <c r="A9" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>52</v>
       </c>
       <c r="E9" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K9" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="L9" s="10">
+      <c r="K9" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="L9" s="6">
         <v>200</v>
       </c>
-      <c r="M9" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>92</v>
+      <c r="M9" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="O9" s="7"/>
     </row>
     <row r="10" ht="139.2" spans="1:15">
       <c r="A10" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>52</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K10" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="L10" s="10">
+      <c r="K10" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L10" s="6">
         <v>200</v>
       </c>
-      <c r="M10" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="N10" s="9" t="s">
-        <v>92</v>
+      <c r="M10" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="O10" s="7"/>
     </row>
     <row r="11" ht="121.8" spans="1:15">
       <c r="A11" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" s="7" t="s">
+      <c r="F11" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K11" s="9" t="s">
+      <c r="K11" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="L11" s="6">
+        <v>200</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="O11" s="7" t="s">
         <v>119</v>
-      </c>
-      <c r="L11" s="10">
-        <v>200</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="12" ht="409.5" spans="1:15">
       <c r="A12" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="7" t="s">
+      <c r="F12" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K12" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="L12" s="10">
+      <c r="K12" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="L12" s="6">
         <v>200</v>
       </c>
-      <c r="M12" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="N12" s="11" t="s">
-        <v>125</v>
+      <c r="M12" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="O12" s="7"/>
     </row>
     <row r="13" ht="121.8" spans="1:15">
       <c r="A13" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" s="7" t="s">
+      <c r="F13" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K13" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="L13" s="10">
+      <c r="K13" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="L13" s="6">
         <v>200</v>
       </c>
-      <c r="M13" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>92</v>
+      <c r="M13" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="O13" s="7"/>
     </row>
     <row r="14" ht="104.4" spans="1:15">
       <c r="A14" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="7" t="s">
+      <c r="F14" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K14" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="L14" s="10">
+      <c r="K14" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="L14" s="6">
         <v>200</v>
       </c>
-      <c r="M14" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="N14" s="11" t="s">
-        <v>132</v>
+      <c r="M14" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>130</v>
       </c>
       <c r="O14" s="7"/>
     </row>
     <row r="15" ht="104.4" spans="1:15">
       <c r="A15" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K15" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="L15" s="10">
+      <c r="K15" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="L15" s="6">
         <v>200</v>
       </c>
-      <c r="M15" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="N15" s="11" t="s">
-        <v>136</v>
+      <c r="M15" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="O15" s="7"/>
     </row>
     <row r="16" ht="139.2" spans="1:15">
       <c r="A16" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="7" t="s">
+      <c r="F16" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K16" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="L16" s="10">
+      <c r="K16" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="L16" s="6">
         <v>200</v>
       </c>
-      <c r="M16" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="N16" s="9" t="s">
-        <v>92</v>
+      <c r="M16" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="O16" s="7"/>
     </row>
     <row r="17" ht="121.8" spans="1:15">
       <c r="A17" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="7" t="s">
+      <c r="F17" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="L17" s="10">
+      <c r="K17" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="L17" s="6">
         <v>200</v>
       </c>
-      <c r="M17" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="N17" s="9" t="s">
-        <v>92</v>
+      <c r="M17" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="O17" s="7"/>
     </row>
-    <row r="18" ht="348" spans="1:15">
+    <row r="18" ht="208.8" spans="1:15">
       <c r="A18" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18" s="7" t="s">
+      <c r="F18" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K18" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="L18" s="10">
+      <c r="K18" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="L18" s="6">
         <v>200</v>
       </c>
-      <c r="M18" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="N18" s="11" t="s">
-        <v>146</v>
+      <c r="M18" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>144</v>
       </c>
       <c r="O18" s="7"/>
     </row>
-    <row r="19" ht="348" spans="1:15">
+    <row r="19" ht="243.6" spans="1:15">
       <c r="A19" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E19" s="7" t="s">
+      <c r="F19" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K19" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="L19" s="10">
+      <c r="K19" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="L19" s="6">
         <v>200</v>
       </c>
-      <c r="M19" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="N19" s="11" t="s">
-        <v>150</v>
+      <c r="M19" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>148</v>
       </c>
       <c r="O19" s="7"/>
     </row>
     <row r="20" ht="121.8" spans="1:15">
       <c r="A20" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="7" t="s">
+      <c r="F20" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K20" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="L20" s="10">
+      <c r="K20" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="L20" s="6">
         <v>200</v>
       </c>
-      <c r="M20" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="N20" s="9" t="s">
-        <v>92</v>
+      <c r="M20" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="O20" s="7"/>
     </row>
     <row r="21" ht="104.4" spans="1:15">
       <c r="A21" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" s="7" t="s">
+      <c r="F21" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G21" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K21" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="L21" s="10">
+      <c r="K21" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="L21" s="6">
         <v>200</v>
       </c>
-      <c r="M21" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="N21" s="11" t="s">
-        <v>132</v>
+      <c r="M21" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>130</v>
       </c>
       <c r="O21" s="7"/>
     </row>
     <row r="22" ht="121.8" spans="1:15">
       <c r="A22" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E22" s="7" t="s">
+      <c r="F22" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G22" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K22" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="L22" s="10">
+      <c r="K22" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="L22" s="6">
         <v>200</v>
       </c>
-      <c r="M22" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="N22" s="9" t="s">
-        <v>92</v>
+      <c r="M22" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="O22" s="7"/>
     </row>
     <row r="23" ht="121.8" spans="1:15">
       <c r="A23" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E23" s="7" t="s">
+      <c r="F23" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G23" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K23" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="L23" s="10">
+      <c r="K23" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="L23" s="6">
         <v>200</v>
       </c>
-      <c r="M23" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="N23" s="9" t="s">
-        <v>92</v>
+      <c r="M23" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="O23" s="7"/>
     </row>
     <row r="24" ht="243.6" spans="1:15">
       <c r="A24" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E24" s="7" t="s">
+      <c r="F24" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K24" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="L24" s="10">
+      <c r="K24" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="L24" s="6">
         <v>200</v>
       </c>
-      <c r="M24" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="N24" s="9" t="s">
-        <v>92</v>
+      <c r="M24" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="O24" s="7"/>
     </row>
     <row r="25" ht="104.4" spans="1:15">
       <c r="A25" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E25" s="7" t="s">
+      <c r="G25" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>26</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K25" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="L25" s="10">
+      <c r="K25" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="L25" s="6">
         <v>200</v>
       </c>
-      <c r="M25" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="N25" s="11" t="s">
-        <v>169</v>
+      <c r="M25" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>167</v>
       </c>
       <c r="O25" s="7"/>
     </row>
